--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3289-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3289-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C9EB646-64D6-419C-8037-093ED8F34C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BD286DF-8392-4CA9-B72D-675177E387F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{AC5B8DDF-E067-42E1-B562-7E8B5CB2C1F7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E268A27F-F014-4D02-8292-C83040AD95DB}"/>
   </bookViews>
   <sheets>
     <sheet name="3289-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1588,22 +1588,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCECFA5-6A42-414B-AE71-0AB820E91A94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC9F558-648A-489F-8895-FC9B083D019B}">
   <dimension ref="A1:R53"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1630,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1661,7 +1660,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1707,7 +1706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1757,7 +1756,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1811,7 +1810,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1837,7 +1836,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1893,7 +1892,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1949,7 +1948,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="51">
         <v>2025</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2059,7 +2058,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2171,7 +2170,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2227,7 +2226,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="53">
         <v>2024</v>
       </c>
@@ -2281,7 +2280,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2337,7 +2336,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2393,7 +2392,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2449,7 +2448,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2505,7 +2504,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
         <v>2023</v>
       </c>
@@ -2559,7 +2558,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2671,7 +2670,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>26</v>
       </c>
@@ -2727,7 +2726,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>26</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>2022</v>
       </c>
@@ -2837,7 +2836,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2949,7 +2948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3005,7 +3004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3061,7 +3060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3117,7 +3116,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="51">
         <v>2021</v>
       </c>
@@ -3171,7 +3170,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>26</v>
       </c>
@@ -3227,7 +3226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
@@ -3283,7 +3282,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>26</v>
       </c>
@@ -3339,7 +3338,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>26</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>26</v>
       </c>
@@ -3451,7 +3450,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="53">
         <v>2020</v>
       </c>
@@ -3505,7 +3504,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="51">
         <v>2019</v>
       </c>
@@ -3559,7 +3558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="53">
         <v>2018</v>
       </c>
@@ -3613,7 +3612,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="51">
         <v>2017</v>
       </c>
@@ -3667,7 +3666,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="53">
         <v>2016</v>
       </c>
@@ -3721,7 +3720,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="51">
         <v>2015</v>
       </c>
@@ -3775,7 +3774,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="53">
         <v>2014</v>
       </c>
@@ -3829,7 +3828,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2013</v>
       </c>
@@ -3883,7 +3882,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="53">
         <v>2012</v>
       </c>
@@ -3937,7 +3936,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="51">
         <v>2011</v>
       </c>
@@ -3991,7 +3990,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="53">
         <v>2010</v>
       </c>
@@ -4045,7 +4044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="51">
         <v>2009</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>7.39</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="53">
         <v>2008</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="51">
         <v>2007</v>
       </c>
@@ -4207,7 +4206,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="53">
         <v>2006</v>
       </c>
@@ -4261,7 +4260,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="51">
         <v>2005</v>
       </c>
@@ -4315,7 +4314,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="53">
         <v>2004</v>
       </c>
@@ -4369,7 +4368,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="51" t="s">
         <v>65</v>
       </c>
